--- a/data/trans_orig/P6715-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6715-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen sentido sus tareas del trabajo en 2012</t>
+          <t>Población según si tienen sentido sus tareas del trabajo en 2012 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -844,97 +844,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2346</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7411</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>8,49%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>2346</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>8112</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>8126</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2346</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>8420</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11592</t>
+          <t>9789</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28873</t>
+          <t>28064</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14271</t>
+          <t>14028</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17129</t>
+          <t>16892</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38395</t>
+          <t>37764</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9959</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25732</t>
+          <t>25395</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11385</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14008</t>
+          <t>14203</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33463</t>
+          <t>32243</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78906</t>
+          <t>80325</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100140</t>
+          <t>101041</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62377</t>
+          <t>61919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77431</t>
+          <t>76896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147806</t>
+          <t>147184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173827</t>
+          <t>173697</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,13%</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>7521</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1526,97 +1526,97 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5319</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>1036</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5272</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>5333</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>5934</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14701</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14085</t>
+          <t>13981</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23785</t>
+          <t>23054</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12510</t>
+          <t>12947</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29878</t>
+          <t>30400</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27903</t>
+          <t>27746</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>28320</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52413</t>
+          <t>52356</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132026</t>
+          <t>131446</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152513</t>
+          <t>151339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84922</t>
+          <t>84600</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104417</t>
+          <t>104924</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>223472</t>
+          <t>224031</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>252738</t>
+          <t>251401</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,24%</t>
         </is>
       </c>
     </row>
@@ -2095,97 +2095,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1881</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4549</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>986</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4074</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>6365</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>986</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4884</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11329</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11219</t>
+          <t>12187</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10544</t>
+          <t>10378</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25890</t>
+          <t>26322</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13237</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28279</t>
+          <t>29474</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26474</t>
+          <t>27298</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48342</t>
+          <t>49528</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27145</t>
+          <t>28616</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48105</t>
+          <t>49085</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13860</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30732</t>
+          <t>29864</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46022</t>
+          <t>45713</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73432</t>
+          <t>71962</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71749</t>
+          <t>70732</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94839</t>
+          <t>93503</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31226</t>
+          <t>30523</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49627</t>
+          <t>48121</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106939</t>
+          <t>106908</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>136661</t>
+          <t>135999</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,56%</t>
         </is>
       </c>
     </row>
@@ -2777,97 +2777,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2073</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2063</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>897</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18293</t>
+          <t>19010</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20258</t>
+          <t>20040</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>14024</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34526</t>
+          <t>32872</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20979</t>
+          <t>20917</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41275</t>
+          <t>41388</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20200</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31783</t>
+          <t>31566</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57558</t>
+          <t>57684</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>89749</t>
+          <t>88934</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>112033</t>
+          <t>112073</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65375</t>
+          <t>66325</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>82958</t>
+          <t>83630</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>161183</t>
+          <t>161111</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>190678</t>
+          <t>191234</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>78,01%</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,62 +3494,62 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>1935</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>5350</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>1051</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>5637</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>898</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>8521</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>877</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9257</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15051</t>
+          <t>14664</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>8048</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21319</t>
+          <t>21275</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>13170</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30857</t>
+          <t>30508</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18976</t>
+          <t>19659</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21657</t>
+          <t>21997</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>18054</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>36647</t>
+          <t>35783</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>53227</t>
+          <t>53577</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>69485</t>
+          <t>69791</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>17058</t>
+          <t>16766</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>31602</t>
+          <t>30877</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>75396</t>
+          <t>76491</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>98540</t>
+          <t>98758</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,59%</t>
         </is>
       </c>
     </row>
@@ -4141,97 +4141,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>2061</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5406</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>20107</t>
+          <t>21054</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12298</t>
+          <t>12118</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>28451</t>
+          <t>28876</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>13610</t>
+          <t>13588</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>31897</t>
+          <t>31960</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>23646</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>28439</t>
+          <t>27383</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>50893</t>
+          <t>50500</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>71957</t>
+          <t>71819</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>91877</t>
+          <t>93584</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>23353</t>
+          <t>23517</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>38940</t>
+          <t>38655</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>101233</t>
+          <t>100716</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>127089</t>
+          <t>125679</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>72,41%</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>896</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>14591</t>
+          <t>14711</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7368</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>16943</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>32028</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>58945</t>
+          <t>57664</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>25877</t>
+          <t>27325</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>48391</t>
+          <t>49614</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>63990</t>
+          <t>64634</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>99430</t>
+          <t>99401</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>34599</t>
+          <t>33350</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>59132</t>
+          <t>58334</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>35776</t>
+          <t>35845</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>59574</t>
+          <t>60816</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>75836</t>
+          <t>75448</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>111805</t>
+          <t>111160</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>157448</t>
+          <t>159580</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>191780</t>
+          <t>190601</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>80320</t>
+          <t>80384</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>108018</t>
+          <t>108846</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>249640</t>
+          <t>247217</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>292869</t>
+          <t>291821</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,26%</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>15130</t>
+          <t>16214</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>16683</t>
+          <t>16828</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>10624</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>27955</t>
+          <t>27505</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>34492</t>
+          <t>34884</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>59555</t>
+          <t>60152</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>27281</t>
+          <t>28671</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>52408</t>
+          <t>52354</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>70054</t>
+          <t>69277</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>104172</t>
+          <t>103362</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>110722</t>
+          <t>111870</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>150334</t>
+          <t>150189</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>65711</t>
+          <t>64047</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>96284</t>
+          <t>95067</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>187754</t>
+          <t>186904</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>235497</t>
+          <t>235033</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>154803</t>
+          <t>154493</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>194572</t>
+          <t>195302</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>111459</t>
+          <t>109981</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>144810</t>
+          <t>144403</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>275292</t>
+          <t>280860</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>329999</t>
+          <t>330987</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,39%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>13477</t>
+          <t>12875</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>12849</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>21148</t>
+          <t>20739</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>14569</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>33731</t>
+          <t>34146</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13717</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>32131</t>
+          <t>32411</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>31570</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>58511</t>
+          <t>57400</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>140828</t>
+          <t>140832</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>190083</t>
+          <t>187550</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>120821</t>
+          <t>119466</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>165256</t>
+          <t>165605</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>271669</t>
+          <t>270698</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>336278</t>
+          <t>338308</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>280558</t>
+          <t>282577</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>346860</t>
+          <t>346216</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>188506</t>
+          <t>190680</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>242265</t>
+          <t>245139</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>483928</t>
+          <t>490877</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>565719</t>
+          <t>568812</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>877969</t>
+          <t>878206</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>951783</t>
+          <t>949987</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>528804</t>
+          <t>524803</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>592315</t>
+          <t>591828</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1429012</t>
+          <t>1428185</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1531251</t>
+          <t>1523844</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen sentido sus tareas del trabajo en 2016</t>
+          <t>Población según si tienen sentido sus tareas del trabajo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>968</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9185</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2295</t>
+          <t>2997</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14503</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16585</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14637</t>
+          <t>13857</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33192</t>
+          <t>32442</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16079</t>
+          <t>15500</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20704</t>
+          <t>21206</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43758</t>
+          <t>43711</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18209</t>
+          <t>18309</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38024</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>16965</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34117</t>
+          <t>34461</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40197</t>
+          <t>40402</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68313</t>
+          <t>67913</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65609</t>
+          <t>66502</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92401</t>
+          <t>90251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53346</t>
+          <t>51336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72710</t>
+          <t>72526</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>123619</t>
+          <t>122779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>155388</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,53%</t>
         </is>
       </c>
     </row>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19262</t>
+          <t>18115</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39150</t>
+          <t>37897</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>18177</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27973</t>
+          <t>28230</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50898</t>
+          <t>52430</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35004</t>
+          <t>34254</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59539</t>
+          <t>58944</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18129</t>
+          <t>17445</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35178</t>
+          <t>35765</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58303</t>
+          <t>58377</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89186</t>
+          <t>88200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79646</t>
+          <t>79995</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106467</t>
+          <t>105604</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63884</t>
+          <t>64890</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84477</t>
+          <t>84596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149520</t>
+          <t>151640</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182476</t>
+          <t>184851</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>65,09%</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9091</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>11389</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -8582,97 +8582,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1822</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>902</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4529</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>4524</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>902</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4484</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18458</t>
+          <t>17766</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16240</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12619</t>
+          <t>11894</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30705</t>
+          <t>28931</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32035</t>
+          <t>31800</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53054</t>
+          <t>52271</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>19368</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35878</t>
+          <t>36995</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55253</t>
+          <t>55642</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81930</t>
+          <t>81597</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60341</t>
+          <t>60802</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82909</t>
+          <t>82912</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36997</t>
+          <t>35420</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54860</t>
+          <t>54561</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>102516</t>
+          <t>103933</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>131695</t>
+          <t>132168</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,72%</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9299,62 +9299,62 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2546</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>9581</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>2546</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>9136</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13653</t>
+          <t>13546</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18425</t>
+          <t>19350</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11092</t>
+          <t>10703</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>27699</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24584</t>
+          <t>22925</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10932</t>
+          <t>10533</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11799</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29480</t>
+          <t>29347</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77179</t>
+          <t>77614</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>96487</t>
+          <t>96983</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>57137</t>
+          <t>55919</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>71157</t>
+          <t>71889</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>139613</t>
+          <t>138266</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>163194</t>
+          <t>163040</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,02%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9868,62 +9868,62 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>1768</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>5863</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>4817</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -9946,97 +9946,97 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1938</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>1768</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>1881</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21430</t>
+          <t>22095</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13158</t>
+          <t>13559</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30085</t>
+          <t>30900</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26203</t>
+          <t>25576</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>44080</t>
+          <t>44297</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21299</t>
+          <t>21182</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>35500</t>
+          <t>35207</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>51791</t>
+          <t>51523</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>75883</t>
+          <t>73981</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>54,26%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>22415</t>
+          <t>22686</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>40521</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13902</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>27877</t>
+          <t>27447</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>39807</t>
+          <t>39764</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>63533</t>
+          <t>61851</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10550,62 +10550,62 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1856</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>5074</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>1011</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>4490</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>16423</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15588</t>
+          <t>15309</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>11714</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27786</t>
+          <t>28708</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>30539</t>
+          <t>31337</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>13367</t>
+          <t>14005</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>29330</t>
+          <t>29116</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>32090</t>
+          <t>31534</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>54485</t>
+          <t>55421</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>25007</t>
+          <t>24674</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>45138</t>
+          <t>44580</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>18794</t>
+          <t>18500</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>35637</t>
+          <t>34052</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>47203</t>
+          <t>47184</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>73189</t>
+          <t>73004</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>30875</t>
+          <t>30838</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>51107</t>
+          <t>50282</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>28388</t>
+          <t>29780</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>47992</t>
+          <t>48783</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>74523</t>
+          <t>74194</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>20962</t>
+          <t>21535</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>15274</t>
+          <t>15974</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>13298</t>
+          <t>12559</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>31449</t>
+          <t>31023</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>21371</t>
+          <t>21635</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>44938</t>
+          <t>43234</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13828</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>32092</t>
+          <t>31798</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>39462</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>67503</t>
+          <t>69075</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>71541</t>
+          <t>71188</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>105454</t>
+          <t>106175</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>53148</t>
+          <t>53129</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>83559</t>
+          <t>82016</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>132337</t>
+          <t>134222</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>179655</t>
+          <t>180303</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>71033</t>
+          <t>70354</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>104804</t>
+          <t>105430</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>57685</t>
+          <t>58862</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>87673</t>
+          <t>87755</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>136782</t>
+          <t>136256</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>182796</t>
+          <t>184445</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>122701</t>
+          <t>121490</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>160665</t>
+          <t>160656</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>99520</t>
+          <t>98150</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>134078</t>
+          <t>131776</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>230985</t>
+          <t>230726</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>283435</t>
+          <t>283272</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>9732</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>11522</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12032,7 +12032,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>11365</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>14790</t>
+          <t>14997</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>33722</t>
+          <t>34507</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>16970</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>36410</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>35048</t>
+          <t>36154</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>62182</t>
+          <t>63995</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>99712</t>
+          <t>98755</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>135419</t>
+          <t>133611</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>64797</t>
+          <t>65213</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>95139</t>
+          <t>93574</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>172976</t>
+          <t>170868</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>218559</t>
+          <t>220851</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>164000</t>
+          <t>163978</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>201109</t>
+          <t>200293</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>116993</t>
+          <t>117043</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>150449</t>
+          <t>148837</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>290531</t>
+          <t>290287</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>337913</t>
+          <t>340542</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,81%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>14845</t>
+          <t>14382</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>34941</t>
+          <t>35524</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>9272</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>26256</t>
+          <t>25272</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>28696</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>54204</t>
+          <t>54310</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>40101</t>
+          <t>41488</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>71694</t>
+          <t>71835</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>26195</t>
+          <t>25640</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>49142</t>
+          <t>49270</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>73917</t>
+          <t>73620</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>115847</t>
+          <t>109854</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>187394</t>
+          <t>185269</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>245956</t>
+          <t>243199</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>136914</t>
+          <t>138073</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>184754</t>
+          <t>184299</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>338013</t>
+          <t>336138</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>408699</t>
+          <t>408330</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>365035</t>
+          <t>370270</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>439389</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>259519</t>
+          <t>261970</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>316957</t>
+          <t>321751</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>643117</t>
+          <t>646749</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>735226</t>
+          <t>739985</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>689035</t>
+          <t>687163</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>765355</t>
+          <t>763921</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>507967</t>
+          <t>501356</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>571463</t>
+          <t>564509</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1213632</t>
+          <t>1209858</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1310511</t>
+          <t>1312738</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13098,12 +13098,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6715-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6715-Provincia-trans_orig.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>8237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8126</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9789</t>
+          <t>10977</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28064</t>
+          <t>28109</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14028</t>
+          <t>15115</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>17091</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37764</t>
+          <t>37768</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9937</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25395</t>
+          <t>26443</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32243</t>
+          <t>32753</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80325</t>
+          <t>79829</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101041</t>
+          <t>100204</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61919</t>
+          <t>63005</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76896</t>
+          <t>77834</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147184</t>
+          <t>147027</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173697</t>
+          <t>173809</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>15042</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13981</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8655</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23054</t>
+          <t>23226</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12947</t>
+          <t>12660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30400</t>
+          <t>30705</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27746</t>
+          <t>27694</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28320</t>
+          <t>27988</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52356</t>
+          <t>51564</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>131446</t>
+          <t>132212</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151339</t>
+          <t>151776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84600</t>
+          <t>84331</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104924</t>
+          <t>104199</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>224031</t>
+          <t>223852</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>251401</t>
+          <t>252088</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11186</t>
+          <t>11327</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12187</t>
+          <t>12028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26322</t>
+          <t>26689</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>12928</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29474</t>
+          <t>28910</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>27298</t>
+          <t>26420</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49528</t>
+          <t>48913</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28616</t>
+          <t>27684</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49085</t>
+          <t>49350</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13860</t>
+          <t>13989</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29864</t>
+          <t>29746</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45713</t>
+          <t>46304</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71962</t>
+          <t>72260</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70732</t>
+          <t>70408</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93503</t>
+          <t>94041</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30523</t>
+          <t>30170</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48121</t>
+          <t>49070</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106908</t>
+          <t>107251</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>135999</t>
+          <t>137704</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>61,31%</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6366</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>899</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19010</t>
+          <t>17804</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20040</t>
+          <t>19538</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14024</t>
+          <t>14283</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32872</t>
+          <t>32532</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20917</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41388</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21271</t>
+          <t>20909</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31566</t>
+          <t>31841</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57684</t>
+          <t>57152</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>88934</t>
+          <t>89397</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>112073</t>
+          <t>112453</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>66325</t>
+          <t>65945</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>83630</t>
+          <t>83220</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>161111</t>
+          <t>160740</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>191234</t>
+          <t>189954</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>7676</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>893</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14664</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>7857</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>21459</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13170</t>
+          <t>13541</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30508</t>
+          <t>30425</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19659</t>
+          <t>18797</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>9297</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21997</t>
+          <t>21701</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>18054</t>
+          <t>17948</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>35783</t>
+          <t>36248</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>53577</t>
+          <t>54247</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>69791</t>
+          <t>70294</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16766</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>30877</t>
+          <t>31647</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>76491</t>
+          <t>75240</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>98758</t>
+          <t>98683</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>28876</t>
+          <t>28092</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>31960</t>
+          <t>32074</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>9957</t>
+          <t>11124</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>24303</t>
+          <t>24453</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>27383</t>
+          <t>26520</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>50500</t>
+          <t>49683</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>71819</t>
+          <t>71939</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>93584</t>
+          <t>92504</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>23517</t>
+          <t>24206</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>38655</t>
+          <t>39426</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>100716</t>
+          <t>101356</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>125679</t>
+          <t>127038</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>73,2%</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4594</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>915</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>14711</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>17210</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>32181</t>
+          <t>32625</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>57664</t>
+          <t>59281</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>27325</t>
+          <t>26127</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>49614</t>
+          <t>49371</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>64634</t>
+          <t>64018</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>99401</t>
+          <t>100373</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>33350</t>
+          <t>33651</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>58334</t>
+          <t>58691</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>35845</t>
+          <t>36660</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>60816</t>
+          <t>59952</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>111160</t>
+          <t>110759</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>159580</t>
+          <t>160130</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>190601</t>
+          <t>193301</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>80384</t>
+          <t>81556</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>108846</t>
+          <t>107277</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>247217</t>
+          <t>248657</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>291821</t>
+          <t>291628</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,22%</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>16214</t>
+          <t>15581</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>18220</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>27505</t>
+          <t>27468</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>34884</t>
+          <t>33677</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>60152</t>
+          <t>59148</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>28671</t>
+          <t>27686</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>52354</t>
+          <t>52276</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>69277</t>
+          <t>67010</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>103362</t>
+          <t>103075</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>111870</t>
+          <t>114484</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>150189</t>
+          <t>152467</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>64047</t>
+          <t>65636</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>95067</t>
+          <t>96977</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>186904</t>
+          <t>186099</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>235033</t>
+          <t>234815</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>154493</t>
+          <t>153817</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>195302</t>
+          <t>193793</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>109981</t>
+          <t>111462</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>144403</t>
+          <t>145684</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>280860</t>
+          <t>277100</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>330987</t>
+          <t>328976</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,07%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6207,77 +6207,77 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>6176</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>2137</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>13422</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>12425</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>7044</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>21531</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
           <t>0,91%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>6176</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>2871</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>12849</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>12425</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>6761</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
-          <t>20739</t>
-        </is>
-      </c>
-      <c r="U52" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="W52" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14133</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>34146</t>
+          <t>33757</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>13484</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>32411</t>
+          <t>32308</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>30440</t>
+          <t>31557</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>57400</t>
+          <t>58657</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>140832</t>
+          <t>140876</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>187550</t>
+          <t>189782</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>119466</t>
+          <t>118568</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>165605</t>
+          <t>165440</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>270698</t>
+          <t>271083</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>338308</t>
+          <t>337885</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>282577</t>
+          <t>282984</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>346216</t>
+          <t>347676</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>190680</t>
+          <t>188304</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>245139</t>
+          <t>245949</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>490877</t>
+          <t>487004</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>568812</t>
+          <t>571375</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>878206</t>
+          <t>878454</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>949987</t>
+          <t>951657</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>524803</t>
+          <t>528088</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>591828</t>
+          <t>591976</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1428185</t>
+          <t>1424726</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1523844</t>
+          <t>1524689</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,49%</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>929</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15145</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13857</t>
+          <t>13982</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32442</t>
+          <t>32729</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>16216</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21206</t>
+          <t>19400</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43711</t>
+          <t>42993</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18309</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38722</t>
+          <t>37407</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16965</t>
+          <t>17034</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34461</t>
+          <t>35163</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40402</t>
+          <t>40430</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67913</t>
+          <t>66605</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66502</t>
+          <t>65790</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90251</t>
+          <t>90710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51336</t>
+          <t>52940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72526</t>
+          <t>72506</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>122779</t>
+          <t>124480</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155388</t>
+          <t>156492</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,99%</t>
         </is>
       </c>
     </row>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7183</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5695</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>9504</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18115</t>
+          <t>18685</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37897</t>
+          <t>39671</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18177</t>
+          <t>18704</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28230</t>
+          <t>27951</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52430</t>
+          <t>51975</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34254</t>
+          <t>34844</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58944</t>
+          <t>58327</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17445</t>
+          <t>18179</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35765</t>
+          <t>35643</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58377</t>
+          <t>57600</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88200</t>
+          <t>88667</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79995</t>
+          <t>79933</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105604</t>
+          <t>106602</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64890</t>
+          <t>62994</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84596</t>
+          <t>84113</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151640</t>
+          <t>150805</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184851</t>
+          <t>183279</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,54%</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>8767</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>974</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11389</t>
+          <t>10099</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17766</t>
+          <t>17732</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>11440</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>29442</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31800</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52271</t>
+          <t>52432</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19368</t>
+          <t>18830</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36995</t>
+          <t>35757</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55642</t>
+          <t>55470</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81597</t>
+          <t>82468</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60802</t>
+          <t>60304</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82912</t>
+          <t>82025</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35420</t>
+          <t>36111</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54561</t>
+          <t>54433</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>103933</t>
+          <t>102567</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>132168</t>
+          <t>131635</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,47%</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8801</t>
+          <t>9164</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13546</t>
+          <t>14964</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19350</t>
+          <t>17745</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27699</t>
+          <t>27437</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6934</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22925</t>
+          <t>24064</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>11114</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29347</t>
+          <t>29503</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77614</t>
+          <t>75585</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>96983</t>
+          <t>96557</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55919</t>
+          <t>56562</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>71889</t>
+          <t>71328</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>138266</t>
+          <t>140250</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>163040</t>
+          <t>164010</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22095</t>
+          <t>21730</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12541</t>
+          <t>12171</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13559</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30900</t>
+          <t>30338</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>25576</t>
+          <t>25999</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>44297</t>
+          <t>43863</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21182</t>
+          <t>21255</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>35207</t>
+          <t>35733</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>51523</t>
+          <t>52545</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>73981</t>
+          <t>75586</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>55,44%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>22686</t>
+          <t>22535</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>40521</t>
+          <t>40727</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>13315</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>27447</t>
+          <t>27387</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>39764</t>
+          <t>40541</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>61851</t>
+          <t>62382</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,75%</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16423</t>
+          <t>16553</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15309</t>
+          <t>16341</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11714</t>
+          <t>11134</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28708</t>
+          <t>27715</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>31337</t>
+          <t>31096</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>14005</t>
+          <t>13358</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>29116</t>
+          <t>29432</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>31534</t>
+          <t>31764</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>55421</t>
+          <t>54732</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>24674</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>44580</t>
+          <t>45137</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>17527</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>34052</t>
+          <t>33105</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>47184</t>
+          <t>47999</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>73004</t>
+          <t>72782</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,76%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>30838</t>
+          <t>31110</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>50282</t>
+          <t>50224</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>13079</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>29780</t>
+          <t>28211</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>48783</t>
+          <t>48475</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>74194</t>
+          <t>74287</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,58%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>21535</t>
+          <t>21106</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>15974</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>12559</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>31023</t>
+          <t>30950</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>21635</t>
+          <t>20722</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>43234</t>
+          <t>44309</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>13828</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>31798</t>
+          <t>31424</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>39127</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>69075</t>
+          <t>68744</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>71188</t>
+          <t>72654</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>106175</t>
+          <t>107335</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>53129</t>
+          <t>53032</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>82016</t>
+          <t>80433</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>134222</t>
+          <t>134576</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>180303</t>
+          <t>179647</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>70354</t>
+          <t>69838</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>105430</t>
+          <t>105234</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>58862</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>87755</t>
+          <t>88379</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>136256</t>
+          <t>136563</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>184445</t>
+          <t>182387</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>121490</t>
+          <t>122137</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>160656</t>
+          <t>161634</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>98150</t>
+          <t>99254</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>131776</t>
+          <t>133074</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>230726</t>
+          <t>230594</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>283272</t>
+          <t>283017</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,89%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>10211</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>11522</t>
+          <t>10766</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>7569</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12032,7 +12032,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>14997</t>
+          <t>13927</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>34507</t>
+          <t>33335</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>17742</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>36670</t>
+          <t>35777</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>36154</t>
+          <t>36347</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>63995</t>
+          <t>64347</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>98755</t>
+          <t>99097</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>133611</t>
+          <t>133816</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>65213</t>
+          <t>64935</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>93574</t>
+          <t>93509</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>170868</t>
+          <t>174871</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>220851</t>
+          <t>219446</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>163978</t>
+          <t>164678</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>200293</t>
+          <t>203572</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>117043</t>
+          <t>118974</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>148837</t>
+          <t>149325</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>290287</t>
+          <t>291038</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>340542</t>
+          <t>341149</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,91%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>35524</t>
+          <t>35474</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,49 +12576,49 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>16260</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>25899</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
           <t>2,5%</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>16260</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>9272</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>25272</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
           <t>37</t>
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>28081</t>
+          <t>28011</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>54310</t>
+          <t>53802</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>41488</t>
+          <t>41094</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>71835</t>
+          <t>70599</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>25640</t>
+          <t>25335</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>49270</t>
+          <t>49680</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>73620</t>
+          <t>72782</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>113345</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>185269</t>
+          <t>186250</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>243199</t>
+          <t>244042</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>138073</t>
+          <t>137120</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>184299</t>
+          <t>184029</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>336138</t>
+          <t>339761</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>408330</t>
+          <t>414218</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>370270</t>
+          <t>367716</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>438466</t>
+          <t>436226</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,49 +12915,49 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
+          <t>30,67%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>288412</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>262100</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>319738</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>27,81%</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>25,27%</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
           <t>30,83%</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>288412</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>261970</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>321751</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>27,81%</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>25,26%</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>31,02%</t>
-        </is>
-      </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
           <t>668</t>
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>646749</t>
+          <t>645287</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>739985</t>
+          <t>735483</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>687163</t>
+          <t>690276</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>763921</t>
+          <t>766886</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>501356</t>
+          <t>504407</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>564509</t>
+          <t>570991</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1209858</t>
+          <t>1212019</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1312738</t>
+          <t>1312523</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
